--- a/UCB.xlsx
+++ b/UCB.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C49160C-BB98-4C6A-9DAA-6CBC72A39DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A7E7DE-85B5-40DF-B882-AAF8C3B39DB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26670" yWindow="1095" windowWidth="26490" windowHeight="19650" xr2:uid="{3A74DB1B-C260-4238-86AA-B6C86577BDB9}"/>
+    <workbookView xWindow="13160" yWindow="4120" windowWidth="19050" windowHeight="16100" xr2:uid="{3A74DB1B-C260-4238-86AA-B6C86577BDB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
+    <sheet name="Model" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
   <si>
     <t>Price EUR</t>
   </si>
@@ -110,7 +111,58 @@
     <t>Nayzilam (midazolam)</t>
   </si>
   <si>
-    <t>Q224</t>
+    <t>MOA</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>1H25</t>
+  </si>
+  <si>
+    <t>2H25</t>
+  </si>
+  <si>
+    <t>1H26</t>
+  </si>
+  <si>
+    <t>2H26</t>
+  </si>
+  <si>
+    <t>Bimzelx</t>
+  </si>
+  <si>
+    <t>Fintepla</t>
+  </si>
+  <si>
+    <t>Rystiggo</t>
+  </si>
+  <si>
+    <t>Zilbrysq</t>
+  </si>
+  <si>
+    <t>Evenity</t>
+  </si>
+  <si>
+    <t>Cimzia</t>
+  </si>
+  <si>
+    <t>Briviact</t>
+  </si>
+  <si>
+    <t>sclerostin mab</t>
+  </si>
+  <si>
+    <t>IL-17A/F mab</t>
+  </si>
+  <si>
+    <t>5HT2B antagonist</t>
   </si>
 </sst>
 </file>
@@ -231,11 +283,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -243,7 +294,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -585,191 +635,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0719C1F-2240-416B-87AB-18B7C02D930D}">
   <dimension ref="B2:K12"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7265625" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.81640625" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B2" s="8" t="s">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="10"/>
+      <c r="D2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="9"/>
       <c r="I2" t="s">
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+        <v>248.7</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="3"/>
       <c r="I3" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="11">
         <v>190</v>
       </c>
-      <c r="K3" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K3" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="3"/>
       <c r="I4" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="11">
         <f>+J2*J3</f>
-        <v>31160</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+        <v>47253</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
+      <c r="G5" s="3"/>
       <c r="I5" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="13">
-        <v>0</v>
-      </c>
-      <c r="K5" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="J5" s="11">
+        <v>7</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="4"/>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="3"/>
       <c r="I6" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="13">
-        <v>2614</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="J6" s="11">
+        <v>0</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="4"/>
+      <c r="G7" s="3"/>
       <c r="I7" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="J7" s="11">
+        <f>+J4-J5+J6</f>
+        <v>47246</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-    </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-    </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="4"/>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B12" s="5" t="s">
+      <c r="G11" s="3"/>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="7"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00D6506C-27B4-4C9E-882F-496D81B1851C}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="11" width="8.7265625" style="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C2" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="10">
+        <v>2024</v>
+      </c>
+      <c r="J2" s="10">
+        <v>2025</v>
+      </c>
+      <c r="K2" s="10">
+        <f>+J2+1</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="10">
+        <v>607</v>
+      </c>
+      <c r="J3" s="10">
+        <v>2227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="10">
+        <v>340</v>
+      </c>
+      <c r="J4" s="10">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="I5" s="10">
+        <v>202</v>
+      </c>
+      <c r="J5" s="10">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6" s="10">
+        <v>72</v>
+      </c>
+      <c r="J6" s="10">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="10">
+        <v>103</v>
+      </c>
+      <c r="J7" s="10">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="10">
+        <v>2033</v>
+      </c>
+      <c r="J8" s="10">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="10">
+        <v>686</v>
+      </c>
+      <c r="J9" s="10">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
